--- a/xls/square_12_tri3_15.xlsx
+++ b/xls/square_12_tri3_15.xlsx
@@ -418,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -482,13 +482,13 @@
         <v>1350</v>
       </c>
       <c r="I15">
-        <v>-1.8043735085334844</v>
+        <v>-1.8043359011994575</v>
       </c>
       <c r="J15">
-        <v>-1.8117104009743585</v>
+        <v>-1.81171044461981</v>
       </c>
       <c r="K15">
-        <v>1.2751575253528915</v>
+        <v>1.2751596804753027</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -517,13 +517,13 @@
         <v>1536</v>
       </c>
       <c r="I16">
-        <v>-2.119240992771276</v>
+        <v>-2.119240425534382</v>
       </c>
       <c r="J16">
-        <v>-1.676968358539173</v>
+        <v>-1.6769683566106623</v>
       </c>
       <c r="K16">
-        <v>1.9861977814565508</v>
+        <v>1.9861977775097608</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -552,13 +552,13 @@
         <v>1734</v>
       </c>
       <c r="I17">
-        <v>-1.528450973106818</v>
+        <v>-1.528450895992042</v>
       </c>
       <c r="J17">
-        <v>-1.2186151755689933</v>
+        <v>-1.2186151202470168</v>
       </c>
       <c r="K17">
-        <v>3.5108598459523663</v>
+        <v>3.5108598361051118</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -587,13 +587,13 @@
         <v>1944</v>
       </c>
       <c r="I18">
-        <v>-0.2544348015195213</v>
+        <v>-0.2544347994690315</v>
       </c>
       <c r="J18">
-        <v>-0.19879077330156153</v>
+        <v>-0.1987907719862113</v>
       </c>
       <c r="K18">
-        <v>3.86149251349462</v>
+        <v>3.8614925115107663</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -622,13 +622,13 @@
         <v>2166</v>
       </c>
       <c r="I19">
-        <v>2.1615988174744545e-5</v>
+        <v>2.161600244945569e-5</v>
       </c>
       <c r="J19">
-        <v>-0.0006541583817010995</v>
+        <v>-0.0006541583754058004</v>
       </c>
       <c r="K19">
-        <v>3.023699793276979</v>
+        <v>3.0236997940083254</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -657,13 +657,13 @@
         <v>2400</v>
       </c>
       <c r="I20">
-        <v>-0.0005942236600137552</v>
+        <v>-0.0005942236610988054</v>
       </c>
       <c r="J20">
-        <v>-0.0008363465762440376</v>
+        <v>-0.0008363465766979036</v>
       </c>
       <c r="K20">
-        <v>2.974906706274974</v>
+        <v>2.9749067061588863</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -692,13 +692,13 @@
         <v>2646</v>
       </c>
       <c r="I21">
-        <v>-9.139493039093472e-5</v>
+        <v>-9.139493039136876e-5</v>
       </c>
       <c r="J21">
-        <v>-6.514198635485033e-5</v>
+        <v>-6.514198635513967e-5</v>
       </c>
       <c r="K21">
-        <v>2.2365132864740063</v>
+        <v>2.236513286524557</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -727,13 +727,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>-0.00032034173405710007</v>
+        <v>-0.0003203417339915257</v>
       </c>
       <c r="J22">
-        <v>-0.000233083395562116</v>
+        <v>-0.00023308339551946985</v>
       </c>
       <c r="K22">
-        <v>2.507588340777333</v>
+        <v>2.5075883409717985</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -762,13 +762,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>-1.5566230637287477e-6</v>
+        <v>-1.5566230619447356e-6</v>
       </c>
       <c r="J23">
-        <v>-4.4105549068410735e-6</v>
+        <v>-4.41055490611782e-6</v>
       </c>
       <c r="K23">
-        <v>1.9249664769320183</v>
+        <v>1.9249664771721455</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -797,13 +797,293 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>-0.00010595126292294672</v>
+        <v>-0.00010595126293770453</v>
       </c>
       <c r="J24">
-        <v>-7.099430420359309e-5</v>
+        <v>-7.0994304212177e-5</v>
       </c>
       <c r="K24">
-        <v>2.2117980299092648</v>
+        <v>2.21179802974548</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25">
+        <v>256</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25">
+        <v>169</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25">
+        <v>676</v>
+      </c>
+      <c r="G25" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25">
+        <v>3750</v>
+      </c>
+      <c r="I25">
+        <v>5.6330575232607215e-6</v>
+      </c>
+      <c r="J25">
+        <v>-8.359663099343882e-7</v>
+      </c>
+      <c r="K25">
+        <v>1.9298875918899157</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26">
+        <v>256</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26">
+        <v>169</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26">
+        <v>729</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26">
+        <v>4056</v>
+      </c>
+      <c r="I26">
+        <v>-8.926571841277315e-6</v>
+      </c>
+      <c r="J26">
+        <v>-6.491211648798899e-6</v>
+      </c>
+      <c r="K26">
+        <v>1.7921003678003395</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27">
+        <v>256</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27">
+        <v>169</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27">
+        <v>784</v>
+      </c>
+      <c r="G27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27">
+        <v>4374</v>
+      </c>
+      <c r="I27">
+        <v>-2.0145246701391538e-5</v>
+      </c>
+      <c r="J27">
+        <v>-1.4512954904090107e-5</v>
+      </c>
+      <c r="K27">
+        <v>1.9270427730086654</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28">
+        <v>256</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28">
+        <v>169</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28">
+        <v>841</v>
+      </c>
+      <c r="G28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28">
+        <v>4704</v>
+      </c>
+      <c r="I28">
+        <v>-8.866751173482294e-6</v>
+      </c>
+      <c r="J28">
+        <v>-7.639191955824292e-6</v>
+      </c>
+      <c r="K28">
+        <v>1.850881550246811</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29">
+        <v>256</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29">
+        <v>169</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29">
+        <v>900</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29">
+        <v>5046</v>
+      </c>
+      <c r="I29">
+        <v>4.717484173745226e-6</v>
+      </c>
+      <c r="J29">
+        <v>7.307489208168123e-7</v>
+      </c>
+      <c r="K29">
+        <v>1.7608855756432347</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30">
+        <v>256</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30">
+        <v>169</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30">
+        <v>961</v>
+      </c>
+      <c r="G30" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30">
+        <v>5400</v>
+      </c>
+      <c r="I30">
+        <v>-2.73086828094531e-5</v>
+      </c>
+      <c r="J30">
+        <v>-1.6891106393217253e-5</v>
+      </c>
+      <c r="K30">
+        <v>1.7981966846048645</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31">
+        <v>256</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31">
+        <v>169</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31">
+        <v>1024</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31">
+        <v>5766</v>
+      </c>
+      <c r="I31">
+        <v>-1.826590405396173e-7</v>
+      </c>
+      <c r="J31">
+        <v>-2.602384820087033e-7</v>
+      </c>
+      <c r="K31">
+        <v>1.2394292246444134</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32">
+        <v>256</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32">
+        <v>169</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32">
+        <v>1089</v>
+      </c>
+      <c r="G32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32">
+        <v>6144</v>
+      </c>
+      <c r="I32">
+        <v>-6.469804844781631e-7</v>
+      </c>
+      <c r="J32">
+        <v>-5.381076708418043e-7</v>
+      </c>
+      <c r="K32">
+        <v>1.2627345597383544</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_12_tri3_15.xlsx
+++ b/xls/square_12_tri3_15.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>256</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <v>169</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13">
+        <v>196</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13">
+        <v>1014</v>
+      </c>
+      <c r="I13">
+        <v>3.6621746132311546</v>
+      </c>
+      <c r="J13">
+        <v>0.19322775671974138</v>
+      </c>
+      <c r="K13">
+        <v>2.8687852193517855</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>256</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14">
+        <v>169</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14">
+        <v>225</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14">
+        <v>1176</v>
+      </c>
+      <c r="I14">
+        <v>2.0554754239807833</v>
+      </c>
+      <c r="J14">
+        <v>-0.8897861715444936</v>
+      </c>
+      <c r="K14">
+        <v>3.1138777221000424</v>
+      </c>
+    </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
         <v>11</v>
